--- a/main/ig/StructureDefinition-fr-cda-performer.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T20:38:51+00:00</t>
+    <t>2026-07-29T12:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-performer.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T12:58:51+00:00</t>
+    <t>2026-08-03T13:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-performer.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:35:26+00:00</t>
+    <t>2026-08-11T08:10:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-performer.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:10:28+00:00</t>
+    <t>2026-08-11T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-performer.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:02+00:00</t>
+    <t>2026-08-28T09:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -528,7 +528,7 @@
     <t>Profession ou rôle du responsable</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS|20260505120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS|20260730120000</t>
   </si>
   <si>
     <t>AssignedEntity.code</t>
